--- a/Excel/MAIN TEMPLATE.xlsx
+++ b/Excel/MAIN TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931CAC51-EAC7-406B-BEAA-414C62405772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D50DC12-0C57-4822-8023-A659130C742B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SAP_Material_Master_Upload" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="154">
   <si>
     <t>Material</t>
   </si>
@@ -430,9 +430,6 @@
     <t>MWST</t>
   </si>
   <si>
-    <t>0001</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -451,16 +448,10 @@
     <t>HALB</t>
   </si>
   <si>
-    <t>HSF004</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
     <t>M3</t>
-  </si>
-  <si>
-    <t>33X37X190</t>
   </si>
   <si>
     <t>SF01</t>
@@ -469,38 +460,35 @@
     <t>S</t>
   </si>
   <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>GT1</t>
-  </si>
-  <si>
     <t>EX</t>
   </si>
   <si>
-    <t>E</t>
+    <t>HSF010</t>
   </si>
   <si>
-    <t>Ini testing Tab pada Material</t>
+    <t>SL. EUCALYPTUS</t>
   </si>
   <si>
-    <t>06</t>
+    <t>45X35X2160</t>
   </si>
   <si>
-    <t>ZWH6</t>
+    <t>ZGF1</t>
   </si>
   <si>
-    <t>C1</t>
+    <t>GF1</t>
   </si>
   <si>
-    <t>4</t>
+    <t>22F3</t>
+  </si>
+  <si>
+    <t>Testing Cut</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="15">
+  <numFmts count="13">
     <numFmt numFmtId="5" formatCode="&quot;Rp&quot;#,##0;\-&quot;Rp&quot;#,##0"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
@@ -514,10 +502,8 @@
     <numFmt numFmtId="170" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="172" formatCode="&quot;Rp&quot;#.##0_);\(&quot;Rp&quot;#.##0\)"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="77">
+  <fonts count="76">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1054,12 +1040,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1369,7 +1349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1689,19 +1669,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -9013,110 +8980,95 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="56" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="56" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="56" borderId="27" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="56" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="56" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -16734,7 +16686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EI2"/>
+  <dimension ref="A1:ED2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -16855,7 +16807,7 @@
     <col min="134" max="134" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" ht="28" customHeight="1">
+    <row r="1" spans="1:134" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17255,50 +17207,40 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:139" s="4" customFormat="1" ht="15.5">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:134" s="3" customFormat="1">
       <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>153</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
+      <c r="K2" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N2" s="3">
+        <v>149</v>
+      </c>
+      <c r="N2" s="2">
         <v>2000</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>2233</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
       <c r="T2" s="3" t="s">
         <v>134</v>
       </c>
@@ -17311,33 +17253,23 @@
       <c r="W2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>136</v>
+      <c r="AD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>1</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="3">
-        <v>200301</v>
+        <v>100301</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AK2" s="3">
-        <v>1.1399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AL2" s="3">
         <v>0</v>
@@ -17346,7 +17278,7 @@
         <v>1</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AO2" s="3">
         <v>0</v>
@@ -17354,185 +17286,81 @@
       <c r="AP2" s="3">
         <v>0</v>
       </c>
-      <c r="AQ2" s="3"/>
       <c r="AR2" s="3">
         <v>0</v>
       </c>
-      <c r="AS2" s="3"/>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3"/>
-      <c r="AV2" s="3"/>
-      <c r="AW2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="3"/>
-      <c r="BB2" s="3"/>
-      <c r="BC2" s="3"/>
-      <c r="BD2" s="3"/>
-      <c r="BE2" s="3"/>
-      <c r="BF2" s="3"/>
       <c r="BG2" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BH2" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="BI2" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BJ2" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BK2" s="3"/>
-      <c r="BL2" s="3"/>
-      <c r="BM2" s="3"/>
+        <v>146</v>
+      </c>
       <c r="BN2" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="BO2" s="3"/>
+        <v>132</v>
+      </c>
       <c r="BP2" s="3">
         <v>1</v>
       </c>
       <c r="BQ2" s="3">
         <v>0</v>
       </c>
-      <c r="BR2" s="3"/>
       <c r="BS2" s="3">
         <v>0</v>
       </c>
       <c r="BT2" s="3">
         <v>0</v>
       </c>
-      <c r="BU2" s="3"/>
       <c r="BV2" s="3">
-        <v>20</v>
-      </c>
-      <c r="BW2" s="3"/>
-      <c r="BX2" s="3"/>
-      <c r="BY2" s="3"/>
+        <v>40</v>
+      </c>
       <c r="BZ2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CB2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="CA2" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="CB2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="CC2" s="3"/>
       <c r="CD2" s="3">
-        <v>1</v>
-      </c>
-      <c r="CE2" s="3"/>
-      <c r="CF2" s="3"/>
-      <c r="CG2" s="3">
-        <v>1207</v>
-      </c>
-      <c r="CH2" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="CF2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="CG2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="CH2" s="3">
+        <v>2</v>
+      </c>
       <c r="CI2" s="3">
         <v>0</v>
       </c>
       <c r="CJ2" s="3">
         <v>0</v>
       </c>
-      <c r="CK2" s="3"/>
       <c r="CL2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="CM2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="CN2" s="3">
         <v>100</v>
       </c>
-      <c r="CO2" s="3"/>
-      <c r="CP2" s="5"/>
-      <c r="CQ2" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="CR2" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="CS2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CT2" s="3"/>
-      <c r="CU2" s="3"/>
-      <c r="CV2" s="3"/>
-      <c r="CW2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CX2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CY2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="CZ2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DA2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DB2" s="3"/>
+      <c r="CQ2" s="3">
+        <v>1</v>
+      </c>
       <c r="DC2" s="3">
         <v>0</v>
       </c>
-      <c r="DD2" s="3"/>
-      <c r="DE2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DF2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DG2" s="3"/>
-      <c r="DH2" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="DI2" s="3">
         <v>0</v>
       </c>
-      <c r="DJ2" s="3"/>
-      <c r="DK2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="DL2" s="3">
-        <v>6</v>
-      </c>
-      <c r="DM2" s="3"/>
-      <c r="DN2" s="3"/>
-      <c r="DO2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="DP2" s="3"/>
-      <c r="DQ2" s="3"/>
-      <c r="DR2" s="3"/>
-      <c r="DS2" s="3"/>
-      <c r="DT2" s="3"/>
-      <c r="DU2" s="3"/>
-      <c r="DV2" s="3"/>
-      <c r="DW2" s="3"/>
-      <c r="DX2" s="3"/>
-      <c r="DY2" s="3"/>
-      <c r="DZ2" s="3"/>
-      <c r="EA2" s="3"/>
-      <c r="EB2" s="3"/>
-      <c r="EC2" s="3"/>
-      <c r="ED2" s="3"/>
-      <c r="EE2" s="2"/>
-      <c r="EF2" s="3"/>
-      <c r="EG2" s="3"/>
-      <c r="EH2" s="3"/>
-      <c r="EI2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
